--- a/AAII_Financials/Quarterly/LGSXY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGSXY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>LGSXY</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -669,52 +669,67 @@
     <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,8 +760,20 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -777,8 +804,20 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +848,20 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,8 +874,12 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -855,8 +910,20 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,8 +954,20 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -919,8 +998,20 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -951,8 +1042,20 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,8 +1065,12 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -994,8 +1101,20 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1026,8 +1145,20 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,8 +1171,12 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1072,8 +1207,20 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1104,8 +1251,20 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1136,8 +1295,20 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1168,8 +1339,20 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1200,8 +1383,20 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,8 +1427,20 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1264,8 +1471,20 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1296,8 +1515,20 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,8 +1559,20 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +1603,20 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1647,20 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,8 +1691,20 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1456,8 +1735,20 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1488,8 +1779,20 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,8 +1823,20 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1552,45 +1867,69 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1942,12 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,211 +1960,287 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>299300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F41" s="3">
+        <v>20100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>64900</v>
+      </c>
+      <c r="H41" s="3">
         <v>28100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>4500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>30000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>3400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>13900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>16300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>60200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>4300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>241900</v>
+      </c>
+      <c r="F42" s="3">
+        <v>297000</v>
+      </c>
+      <c r="G42" s="3">
+        <v>430700</v>
+      </c>
+      <c r="H42" s="3">
         <v>554800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="I42" s="3">
         <v>623400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="J42" s="3">
         <v>469500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="K42" s="3">
         <v>437200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="L42" s="3">
         <v>485000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="M42" s="3">
         <v>467200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="N42" s="3">
         <v>372000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="O42" s="3">
         <v>339600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="P42" s="3">
         <v>338300</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>386800</v>
+        <v>730800</v>
       </c>
       <c r="E43" s="3">
+        <v>563800</v>
+      </c>
+      <c r="F43" s="3">
+        <v>505900</v>
+      </c>
+      <c r="G43" s="3">
+        <v>449900</v>
+      </c>
+      <c r="H43" s="3">
+        <v>446800</v>
+      </c>
+      <c r="I43" s="3">
         <v>652900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>555100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>537400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>518500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>577700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>602100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>335900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>334100</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>19000</v>
+      </c>
+      <c r="F44" s="3">
+        <v>16700</v>
+      </c>
+      <c r="G44" s="3">
+        <v>17100</v>
+      </c>
+      <c r="H44" s="3">
         <v>14900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="I44" s="3">
         <v>15300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="J44" s="3">
         <v>13000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="K44" s="3">
         <v>12300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>12000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>12900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>11700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>11700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>199700</v>
+        <v>133600</v>
       </c>
       <c r="E45" s="3">
+        <v>106200</v>
+      </c>
+      <c r="F45" s="3">
+        <v>121200</v>
+      </c>
+      <c r="G45" s="3">
+        <v>126500</v>
+      </c>
+      <c r="H45" s="3">
+        <v>139700</v>
+      </c>
+      <c r="I45" s="3">
         <v>173000</v>
       </c>
-      <c r="F45" s="3">
-        <v>85700</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="J45" s="3">
+        <v>49400</v>
+      </c>
+      <c r="K45" s="3">
         <v>35700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>38500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>44900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>47300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>210800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>131800</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1248000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>960500</v>
+      </c>
+      <c r="F46" s="3">
+        <v>964500</v>
+      </c>
+      <c r="G46" s="3">
+        <v>1094200</v>
+      </c>
+      <c r="H46" s="3">
         <v>1189700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>1474600</v>
       </c>
-      <c r="F46" s="3">
-        <v>1157500</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
+        <v>1121100</v>
+      </c>
+      <c r="K46" s="3">
         <v>1030400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>1067900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>1125400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>1099200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>902400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>847200</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>700</v>
+        <v>36400</v>
       </c>
       <c r="E47" s="3">
-        <v>600</v>
+        <v>37700</v>
       </c>
       <c r="F47" s="3">
-        <v>600</v>
+        <v>36900</v>
       </c>
       <c r="G47" s="3">
         <v>700</v>
@@ -1830,83 +2249,119 @@
         <v>700</v>
       </c>
       <c r="I47" s="3">
+        <v>600</v>
+      </c>
+      <c r="J47" s="3">
+        <v>37000</v>
+      </c>
+      <c r="K47" s="3">
+        <v>700</v>
+      </c>
+      <c r="L47" s="3">
+        <v>700</v>
+      </c>
+      <c r="M47" s="3">
         <v>800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>8700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>463700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>462800</v>
+      </c>
+      <c r="F48" s="3">
+        <v>446400</v>
+      </c>
+      <c r="G48" s="3">
+        <v>449800</v>
+      </c>
+      <c r="H48" s="3">
         <v>433300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
         <v>399700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>369500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>405900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>393700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>440600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>458600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>437900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>454900</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2424700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2316500</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2159500</v>
+      </c>
+      <c r="G49" s="3">
+        <v>207200</v>
+      </c>
+      <c r="H49" s="3">
         <v>2140000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="I49" s="3">
         <v>1993900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="J49" s="3">
         <v>1811200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="K49" s="3">
         <v>2024500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>1977300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>2167200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>2225200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>2080300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>2122000</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2392,20 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2436,64 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>791900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>704900</v>
+      </c>
+      <c r="F52" s="3">
+        <v>689200</v>
+      </c>
+      <c r="G52" s="3">
+        <v>2690600</v>
+      </c>
+      <c r="H52" s="3">
         <v>648100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="I52" s="3">
         <v>447200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="J52" s="3">
         <v>424500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="K52" s="3">
         <v>479100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>496800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>572800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>618900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>665600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>788900</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2524,64 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5868400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5421600</v>
+      </c>
+      <c r="F54" s="3">
+        <v>4672000</v>
+      </c>
+      <c r="G54" s="3">
+        <v>4830500</v>
+      </c>
+      <c r="H54" s="3">
         <v>4800100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>4681400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>4097700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>4377100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>4362300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>4745300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>4887800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>4677900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>4854100</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2594,12 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,200 +2612,276 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>405800</v>
+        <v>413900</v>
       </c>
       <c r="E57" s="3">
+        <v>477000</v>
+      </c>
+      <c r="F57" s="3">
+        <v>436700</v>
+      </c>
+      <c r="G57" s="3">
+        <v>367900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>345600</v>
+      </c>
+      <c r="I57" s="3">
         <v>339200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>315500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>240700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>235700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>264200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>289000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>238700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>220800</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>114200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>250500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>233100</v>
+      </c>
+      <c r="G58" s="3">
+        <v>243000</v>
+      </c>
+      <c r="H58" s="3">
         <v>228800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="I58" s="3">
         <v>150100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="J58" s="3">
         <v>124100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="K58" s="3">
         <v>2126800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="L58" s="3">
         <v>2074100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="M58" s="3">
         <v>2345700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>2342600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>2253600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>2286500</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>305400</v>
+        <v>328600</v>
       </c>
       <c r="E59" s="3">
+        <v>439100</v>
+      </c>
+      <c r="F59" s="3">
+        <v>305300</v>
+      </c>
+      <c r="G59" s="3">
+        <v>296300</v>
+      </c>
+      <c r="H59" s="3">
+        <v>299600</v>
+      </c>
+      <c r="I59" s="3">
         <v>401900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="J59" s="3">
         <v>245300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="K59" s="3">
         <v>224500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>244200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>301200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>396000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>363800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>425200</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1076600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1364800</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1181200</v>
+      </c>
+      <c r="G60" s="3">
+        <v>1105000</v>
+      </c>
+      <c r="H60" s="3">
         <v>1034800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>1024400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>814000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>2749400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>2695300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>3079400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>3195300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>3063400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>3126800</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1726100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1691400</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1595600</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1613500</v>
+      </c>
+      <c r="H61" s="3">
         <v>1604400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>1642500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>1460800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="K61" s="3">
         <v>169000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>195700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>40200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>41200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>39600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1179900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>678400</v>
+      </c>
+      <c r="F62" s="3">
+        <v>815200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>960000</v>
+      </c>
+      <c r="H62" s="3">
         <v>1036600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="I62" s="3">
         <v>941500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="J62" s="3">
         <v>904900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="K62" s="3">
         <v>854800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>911000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>1001100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>930300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>880800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>962400</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2912,20 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2956,20 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +3000,64 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4071400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3826200</v>
+      </c>
+      <c r="F66" s="3">
+        <v>3682800</v>
+      </c>
+      <c r="G66" s="3">
+        <v>3775600</v>
+      </c>
+      <c r="H66" s="3">
         <v>3774300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>3697800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>3253900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>3854100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>3878100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>4199200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>4249800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>4067500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>4219400</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +3070,12 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +3106,20 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +3150,20 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +3194,20 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,40 +3238,64 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>426500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>471200</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-66600</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-34300</v>
+      </c>
+      <c r="H72" s="3">
         <v>-40200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="I72" s="3">
         <v>-29800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>-96000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>-457700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>-478200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>-519700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>-464300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>-461700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>-476700</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +3326,20 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +3370,20 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +3414,64 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1797000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1595500</v>
+      </c>
+      <c r="F76" s="3">
+        <v>989200</v>
+      </c>
+      <c r="G76" s="3">
+        <v>1054900</v>
+      </c>
+      <c r="H76" s="3">
         <v>1025700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>983600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>843700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>523000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>484200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>546100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>638000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>610400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>634700</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,45 +3502,69 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2816,8 +3595,20 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,40 +3621,56 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5800</v>
+        <v>41900</v>
       </c>
       <c r="E83" s="3">
-        <v>42000</v>
+        <v>38300</v>
       </c>
       <c r="F83" s="3">
-        <v>41400</v>
+        <v>41200</v>
       </c>
       <c r="G83" s="3">
         <v>39500</v>
       </c>
       <c r="H83" s="3">
+        <v>38500</v>
+      </c>
+      <c r="I83" s="3">
+        <v>42000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>41400</v>
+      </c>
+      <c r="K83" s="3">
+        <v>39500</v>
+      </c>
+      <c r="L83" s="3">
         <v>40700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="M83" s="3">
         <v>38000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="N83" s="3">
         <v>4900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="O83" s="3">
         <v>4900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="P83" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3701,20 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3745,20 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3789,20 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3833,20 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3877,64 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-88600</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="H89" s="3">
         <v>39200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="I89" s="3">
         <v>132200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="J89" s="3">
         <v>179600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>12500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>102600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>80200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>105100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>48800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>84800</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3947,56 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="H91" s="3">
         <v>-7200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="J91" s="3">
         <v>-11800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="K91" s="3">
         <v>-5700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-3600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-11500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +4027,20 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +4071,64 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>54600</v>
+      </c>
+      <c r="F94" s="3">
+        <v>54900</v>
+      </c>
+      <c r="G94" s="3">
+        <v>96600</v>
+      </c>
+      <c r="H94" s="3">
         <v>38800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="I94" s="3">
         <v>-156800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="J94" s="3">
         <v>-121700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="K94" s="3">
         <v>22300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>-98300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>-119000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>-46400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>-40400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>-35100</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,8 +4141,12 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3242,8 +4177,20 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +4221,20 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +4265,20 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +4309,64 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="H100" s="3">
         <v>-54600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="I100" s="3">
         <v>-3300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="J100" s="3">
         <v>-30800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="K100" s="3">
         <v>-45400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>-5100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>-3100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>-2900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>-28000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>-30600</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3402,36 +4397,60 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>269500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="G102" s="3">
+        <v>36200</v>
+      </c>
+      <c r="H102" s="3">
         <v>23400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="I102" s="3">
         <v>-27900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="J102" s="3">
         <v>27000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>-10700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>-42000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>55800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>-19600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>19000</v>
       </c>
     </row>
